--- a/scripts/codemagic-ci/testing/Regression-Test-Plan-Template-iOS-QA.xlsx
+++ b/scripts/codemagic-ci/testing/Regression-Test-Plan-Template-iOS-QA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27109"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cbryant/UCSD/campusmobile/scripts/codemagic-ci/testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{A5F54809-0F9A-454A-951E-3620849452A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79EFE39F-623A-4BE0-A5D6-52FECF30DE5C}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{A5F54809-0F9A-454A-951E-3620849452A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C2077FC-9B2B-4A3E-ADCD-7AB5FDD2AD05}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="77">
   <si>
     <t xml:space="preserve">Regression Test Plan - ${APP_VERSION} - ${BUILD_ENV}  </t>
   </si>
@@ -213,30 +213,6 @@
   </si>
   <si>
     <t>Platform Duty Cycle - ESR iPaaS - UCSD Collab (atlassian.net)</t>
-  </si>
-  <si>
-    <t>Native Scanner (not logged in) link navigates to Profile SSO Login</t>
-  </si>
-  <si>
-    <t>Native Scanner (logged in) link launches Scandit Native Scanner</t>
-  </si>
-  <si>
-    <t>Native Scanner Code128 submission successful and verified</t>
-  </si>
-  <si>
-    <t>Native Scanner Code128 submission failed - duplicate barcode</t>
-  </si>
-  <si>
-    <t>Native Scanner Code128 submission failed - invalid barcode</t>
-  </si>
-  <si>
-    <t>Native Scanner 2D submission successful and verified</t>
-  </si>
-  <si>
-    <t>Native Scanner 2D submission failed - duplicate barcode</t>
-  </si>
-  <si>
-    <t>Native Scanner 2D submission failed - invalid barcode</t>
   </si>
   <si>
     <t>MyStudentChart card launches device browser, loads MyStudentChart login site</t>
@@ -1003,7 +979,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:V982" headerRowCount="0" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A1:V974" headerRowCount="0" headerRowDxfId="24" dataDxfId="23" totalsRowDxfId="22">
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1" dataDxfId="21"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Column3" dataDxfId="20"/>
@@ -1238,7 +1214,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:V982"/>
+  <dimension ref="A1:V974"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="96.5703125" style="6" customWidth="1"/>
@@ -1908,6 +1884,7 @@
       <c r="B24" s="38"/>
       <c r="C24" s="38"/>
       <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
@@ -1933,6 +1910,7 @@
       <c r="B25" s="38"/>
       <c r="C25" s="38"/>
       <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
@@ -1958,6 +1936,7 @@
       <c r="B26" s="38"/>
       <c r="C26" s="38"/>
       <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -1983,6 +1962,7 @@
       <c r="B27" s="38"/>
       <c r="C27" s="38"/>
       <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -2008,6 +1988,7 @@
       <c r="B28" s="38"/>
       <c r="C28" s="38"/>
       <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
@@ -2032,10 +2013,10 @@
       </c>
       <c r="B29" s="38"/>
       <c r="C29" s="38"/>
-      <c r="D29" s="1"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
@@ -2058,6 +2039,7 @@
       <c r="B30" s="38"/>
       <c r="C30" s="38"/>
       <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -2129,11 +2111,11 @@
       <c r="V32" s="1"/>
     </row>
     <row r="33" spans="1:22">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="B33" s="38"/>
-      <c r="C33" s="38"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="39"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -2155,7 +2137,7 @@
       <c r="V33" s="1"/>
     </row>
     <row r="34" spans="1:22">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="6" t="s">
         <v>58</v>
       </c>
       <c r="B34" s="38"/>
@@ -2181,7 +2163,7 @@
       <c r="V34" s="1"/>
     </row>
     <row r="35" spans="1:22">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="6" t="s">
         <v>59</v>
       </c>
       <c r="B35" s="38"/>
@@ -2207,7 +2189,7 @@
       <c r="V35" s="1"/>
     </row>
     <row r="36" spans="1:22">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="6" t="s">
         <v>60</v>
       </c>
       <c r="B36" s="38"/>
@@ -2233,15 +2215,16 @@
       <c r="V36" s="1"/>
     </row>
     <row r="37" spans="1:22">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B37" s="38"/>
       <c r="C37" s="38"/>
-      <c r="D37" s="8"/>
+      <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
@@ -2258,7 +2241,7 @@
       <c r="V37" s="1"/>
     </row>
     <row r="38" spans="1:22">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B38" s="38"/>
@@ -2284,7 +2267,7 @@
       <c r="V38" s="1"/>
     </row>
     <row r="39" spans="1:22">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="6" t="s">
         <v>63</v>
       </c>
       <c r="B39" s="38"/>
@@ -2310,7 +2293,7 @@
       <c r="V39" s="1"/>
     </row>
     <row r="40" spans="1:22">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="6" t="s">
         <v>64</v>
       </c>
       <c r="B40" s="38"/>
@@ -2336,7 +2319,7 @@
       <c r="V40" s="1"/>
     </row>
     <row r="41" spans="1:22">
-      <c r="A41" s="28" t="s">
+      <c r="A41" s="27" t="s">
         <v>65</v>
       </c>
       <c r="B41" s="39"/>
@@ -2362,7 +2345,7 @@
       <c r="V41" s="1"/>
     </row>
     <row r="42" spans="1:22">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="5" t="s">
         <v>66</v>
       </c>
       <c r="B42" s="38"/>
@@ -2388,7 +2371,7 @@
       <c r="V42" s="1"/>
     </row>
     <row r="43" spans="1:22">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B43" s="38"/>
@@ -2414,7 +2397,7 @@
       <c r="V43" s="1"/>
     </row>
     <row r="44" spans="1:22">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="5" t="s">
         <v>68</v>
       </c>
       <c r="B44" s="38"/>
@@ -2440,11 +2423,11 @@
       <c r="V44" s="1"/>
     </row>
     <row r="45" spans="1:22">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="27" t="s">
         <v>69</v>
       </c>
-      <c r="B45" s="38"/>
-      <c r="C45" s="38"/>
+      <c r="B45" s="39"/>
+      <c r="C45" s="39"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -2466,7 +2449,7 @@
       <c r="V45" s="1"/>
     </row>
     <row r="46" spans="1:22">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="5" t="s">
         <v>70</v>
       </c>
       <c r="B46" s="38"/>
@@ -2492,7 +2475,7 @@
       <c r="V46" s="1"/>
     </row>
     <row r="47" spans="1:22">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="5" t="s">
         <v>71</v>
       </c>
       <c r="B47" s="38"/>
@@ -2518,7 +2501,7 @@
       <c r="V47" s="1"/>
     </row>
     <row r="48" spans="1:22">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="5" t="s">
         <v>72</v>
       </c>
       <c r="B48" s="38"/>
@@ -2544,11 +2527,11 @@
       <c r="V48" s="1"/>
     </row>
     <row r="49" spans="1:22">
-      <c r="A49" s="27" t="s">
+      <c r="A49" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B49" s="39"/>
-      <c r="C49" s="39"/>
+      <c r="B49" s="38"/>
+      <c r="C49" s="38"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="1"/>
@@ -2570,11 +2553,11 @@
       <c r="V49" s="1"/>
     </row>
     <row r="50" spans="1:22">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="B50" s="38"/>
-      <c r="C50" s="38"/>
+      <c r="B50" s="39"/>
+      <c r="C50" s="39"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
@@ -2596,11 +2579,11 @@
       <c r="V50" s="1"/>
     </row>
     <row r="51" spans="1:22">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="B51" s="38"/>
-      <c r="C51" s="38"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="30"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
@@ -2621,12 +2604,12 @@
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
     </row>
-    <row r="52" spans="1:22">
-      <c r="A52" s="5" t="s">
+    <row r="52" spans="1:22" ht="28.5">
+      <c r="A52" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="B52" s="38"/>
-      <c r="C52" s="38"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="30"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
@@ -2648,11 +2631,9 @@
       <c r="V52" s="1"/>
     </row>
     <row r="53" spans="1:22">
-      <c r="A53" s="27" t="s">
-        <v>77</v>
-      </c>
-      <c r="B53" s="39"/>
-      <c r="C53" s="39"/>
+      <c r="A53" s="5"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="30"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -2674,11 +2655,9 @@
       <c r="V53" s="1"/>
     </row>
     <row r="54" spans="1:22">
-      <c r="A54" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="B54" s="38"/>
-      <c r="C54" s="38"/>
+      <c r="A54" s="5"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="30"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
@@ -2700,11 +2679,9 @@
       <c r="V54" s="1"/>
     </row>
     <row r="55" spans="1:22">
-      <c r="A55" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B55" s="38"/>
-      <c r="C55" s="38"/>
+      <c r="A55" s="5"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="30"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
@@ -2726,11 +2703,9 @@
       <c r="V55" s="1"/>
     </row>
     <row r="56" spans="1:22">
-      <c r="A56" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B56" s="38"/>
-      <c r="C56" s="38"/>
+      <c r="A56" s="5"/>
+      <c r="B56" s="21"/>
+      <c r="C56" s="30"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
@@ -2752,11 +2727,9 @@
       <c r="V56" s="1"/>
     </row>
     <row r="57" spans="1:22">
-      <c r="A57" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B57" s="38"/>
-      <c r="C57" s="38"/>
+      <c r="A57" s="5"/>
+      <c r="B57" s="21"/>
+      <c r="C57" s="30"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
@@ -2778,11 +2751,9 @@
       <c r="V57" s="1"/>
     </row>
     <row r="58" spans="1:22">
-      <c r="A58" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="B58" s="39"/>
-      <c r="C58" s="39"/>
+      <c r="A58" s="5"/>
+      <c r="B58" s="21"/>
+      <c r="C58" s="30"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
@@ -2804,9 +2775,7 @@
       <c r="V58" s="1"/>
     </row>
     <row r="59" spans="1:22">
-      <c r="A59" s="20" t="s">
-        <v>83</v>
-      </c>
+      <c r="A59" s="5"/>
       <c r="B59" s="21"/>
       <c r="C59" s="30"/>
       <c r="D59" s="1"/>
@@ -2830,9 +2799,7 @@
       <c r="V59" s="1"/>
     </row>
     <row r="60" spans="1:22" ht="31.5" customHeight="1">
-      <c r="A60" s="40" t="s">
-        <v>84</v>
-      </c>
+      <c r="A60" s="5"/>
       <c r="B60" s="21"/>
       <c r="C60" s="30"/>
       <c r="D60" s="1"/>
@@ -24791,198 +24758,6 @@
       <c r="U974" s="1"/>
       <c r="V974" s="1"/>
     </row>
-    <row r="975" spans="1:22">
-      <c r="A975" s="5"/>
-      <c r="B975" s="21"/>
-      <c r="C975" s="30"/>
-      <c r="D975" s="1"/>
-      <c r="E975" s="1"/>
-      <c r="F975" s="1"/>
-      <c r="G975" s="1"/>
-      <c r="H975" s="1"/>
-      <c r="I975" s="1"/>
-      <c r="J975" s="1"/>
-      <c r="K975" s="1"/>
-      <c r="L975" s="1"/>
-      <c r="M975" s="1"/>
-      <c r="N975" s="1"/>
-      <c r="O975" s="1"/>
-      <c r="P975" s="1"/>
-      <c r="Q975" s="1"/>
-      <c r="R975" s="1"/>
-      <c r="S975" s="1"/>
-      <c r="T975" s="1"/>
-      <c r="U975" s="1"/>
-      <c r="V975" s="1"/>
-    </row>
-    <row r="976" spans="1:22">
-      <c r="A976" s="5"/>
-      <c r="B976" s="21"/>
-      <c r="C976" s="30"/>
-      <c r="D976" s="1"/>
-      <c r="E976" s="1"/>
-      <c r="F976" s="1"/>
-      <c r="G976" s="1"/>
-      <c r="H976" s="1"/>
-      <c r="I976" s="1"/>
-      <c r="J976" s="1"/>
-      <c r="K976" s="1"/>
-      <c r="L976" s="1"/>
-      <c r="M976" s="1"/>
-      <c r="N976" s="1"/>
-      <c r="O976" s="1"/>
-      <c r="P976" s="1"/>
-      <c r="Q976" s="1"/>
-      <c r="R976" s="1"/>
-      <c r="S976" s="1"/>
-      <c r="T976" s="1"/>
-      <c r="U976" s="1"/>
-      <c r="V976" s="1"/>
-    </row>
-    <row r="977" spans="1:22">
-      <c r="A977" s="5"/>
-      <c r="B977" s="21"/>
-      <c r="C977" s="30"/>
-      <c r="D977" s="1"/>
-      <c r="E977" s="1"/>
-      <c r="F977" s="1"/>
-      <c r="G977" s="1"/>
-      <c r="H977" s="1"/>
-      <c r="I977" s="1"/>
-      <c r="J977" s="1"/>
-      <c r="K977" s="1"/>
-      <c r="L977" s="1"/>
-      <c r="M977" s="1"/>
-      <c r="N977" s="1"/>
-      <c r="O977" s="1"/>
-      <c r="P977" s="1"/>
-      <c r="Q977" s="1"/>
-      <c r="R977" s="1"/>
-      <c r="S977" s="1"/>
-      <c r="T977" s="1"/>
-      <c r="U977" s="1"/>
-      <c r="V977" s="1"/>
-    </row>
-    <row r="978" spans="1:22">
-      <c r="A978" s="5"/>
-      <c r="B978" s="21"/>
-      <c r="C978" s="30"/>
-      <c r="D978" s="1"/>
-      <c r="E978" s="1"/>
-      <c r="F978" s="1"/>
-      <c r="G978" s="1"/>
-      <c r="H978" s="1"/>
-      <c r="I978" s="1"/>
-      <c r="J978" s="1"/>
-      <c r="K978" s="1"/>
-      <c r="L978" s="1"/>
-      <c r="M978" s="1"/>
-      <c r="N978" s="1"/>
-      <c r="O978" s="1"/>
-      <c r="P978" s="1"/>
-      <c r="Q978" s="1"/>
-      <c r="R978" s="1"/>
-      <c r="S978" s="1"/>
-      <c r="T978" s="1"/>
-      <c r="U978" s="1"/>
-      <c r="V978" s="1"/>
-    </row>
-    <row r="979" spans="1:22">
-      <c r="A979" s="5"/>
-      <c r="B979" s="21"/>
-      <c r="C979" s="30"/>
-      <c r="D979" s="1"/>
-      <c r="E979" s="1"/>
-      <c r="F979" s="1"/>
-      <c r="G979" s="1"/>
-      <c r="H979" s="1"/>
-      <c r="I979" s="1"/>
-      <c r="J979" s="1"/>
-      <c r="K979" s="1"/>
-      <c r="L979" s="1"/>
-      <c r="M979" s="1"/>
-      <c r="N979" s="1"/>
-      <c r="O979" s="1"/>
-      <c r="P979" s="1"/>
-      <c r="Q979" s="1"/>
-      <c r="R979" s="1"/>
-      <c r="S979" s="1"/>
-      <c r="T979" s="1"/>
-      <c r="U979" s="1"/>
-      <c r="V979" s="1"/>
-    </row>
-    <row r="980" spans="1:22">
-      <c r="A980" s="5"/>
-      <c r="B980" s="21"/>
-      <c r="C980" s="30"/>
-      <c r="D980" s="1"/>
-      <c r="E980" s="1"/>
-      <c r="F980" s="1"/>
-      <c r="G980" s="1"/>
-      <c r="H980" s="1"/>
-      <c r="I980" s="1"/>
-      <c r="J980" s="1"/>
-      <c r="K980" s="1"/>
-      <c r="L980" s="1"/>
-      <c r="M980" s="1"/>
-      <c r="N980" s="1"/>
-      <c r="O980" s="1"/>
-      <c r="P980" s="1"/>
-      <c r="Q980" s="1"/>
-      <c r="R980" s="1"/>
-      <c r="S980" s="1"/>
-      <c r="T980" s="1"/>
-      <c r="U980" s="1"/>
-      <c r="V980" s="1"/>
-    </row>
-    <row r="981" spans="1:22">
-      <c r="A981" s="5"/>
-      <c r="B981" s="21"/>
-      <c r="C981" s="30"/>
-      <c r="D981" s="1"/>
-      <c r="E981" s="1"/>
-      <c r="F981" s="1"/>
-      <c r="G981" s="1"/>
-      <c r="H981" s="1"/>
-      <c r="I981" s="1"/>
-      <c r="J981" s="1"/>
-      <c r="K981" s="1"/>
-      <c r="L981" s="1"/>
-      <c r="M981" s="1"/>
-      <c r="N981" s="1"/>
-      <c r="O981" s="1"/>
-      <c r="P981" s="1"/>
-      <c r="Q981" s="1"/>
-      <c r="R981" s="1"/>
-      <c r="S981" s="1"/>
-      <c r="T981" s="1"/>
-      <c r="U981" s="1"/>
-      <c r="V981" s="1"/>
-    </row>
-    <row r="982" spans="1:22">
-      <c r="A982" s="5"/>
-      <c r="B982" s="21"/>
-      <c r="C982" s="30"/>
-      <c r="D982" s="1"/>
-      <c r="E982" s="1"/>
-      <c r="F982" s="1"/>
-      <c r="G982" s="1"/>
-      <c r="H982" s="1"/>
-      <c r="I982" s="1"/>
-      <c r="J982" s="1"/>
-      <c r="K982" s="1"/>
-      <c r="L982" s="1"/>
-      <c r="M982" s="1"/>
-      <c r="N982" s="1"/>
-      <c r="O982" s="1"/>
-      <c r="P982" s="1"/>
-      <c r="Q982" s="1"/>
-      <c r="R982" s="1"/>
-      <c r="S982" s="1"/>
-      <c r="T982" s="1"/>
-      <c r="U982" s="1"/>
-      <c r="V982" s="1"/>
-    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
@@ -25003,10 +24778,19 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100231ACC10D748F34BAA0C20ABFA72A7EA" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5b60ada5ef74d917189c377d37311689">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a56c8121-053f-455f-842b-cd566811d075" xmlns:ns3="76f06672-c643-4888-a225-c4422b0e89ee" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f62d863a5068cb9de04048c4fc264cf7" ns2:_="" ns3:_="">
-    <xsd:import namespace="a56c8121-053f-455f-842b-cd566811d075"/>
-    <xsd:import namespace="76f06672-c643-4888-a225-c4422b0e89ee"/>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F5D778AC6A79A84EAA5B25C5A2BFF7B6" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="dba055ea2ef6f995fa2b93dd0ece404c">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3cd0eaed-44fe-4f97-8632-c05a782ebbb7" xmlns:ns3="75164c79-2692-43d6-94a7-34b44bf80abd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f036b67ea408c255de0ae726e51a87d7" ns2:_="" ns3:_="">
+    <xsd:import namespace="3cd0eaed-44fe-4f97-8632-c05a782ebbb7"/>
+    <xsd:import namespace="75164c79-2692-43d6-94a7-34b44bf80abd"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -25015,11 +24799,11 @@
               <xsd:all>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -25027,7 +24811,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="a56c8121-053f-455f-842b-cd566811d075" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3cd0eaed-44fe-4f97-8632-c05a782ebbb7" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -25040,26 +24824,26 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="11" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="13" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="12" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="14" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="76f06672-c643-4888-a225-c4422b0e89ee" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="75164c79-2692-43d6-94a7-34b44bf80abd" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="13" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -25078,7 +24862,7 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="14" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
@@ -25185,15 +24969,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -25201,11 +24976,11 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C37A5DE0-9FD1-4721-9C30-3A5B42A32EC8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AF01965-4B53-4043-B5ED-A531E4D3A7B2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AF01965-4B53-4043-B5ED-A531E4D3A7B2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B3AD93E-3F67-49FE-A0A7-463CF378AD97}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
